--- a/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
+++ b/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="107">
   <si>
     <t>Lox, Stocks and 2 Skattebooms!</t>
   </si>
@@ -52,7 +52,136 @@
     <t>Walnut Rushers</t>
   </si>
   <si>
-    <t>0-3-0</t>
+    <t>0-4-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>1-2-1</t>
+  </si>
+  <si>
+    <t>2-1-1</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Wins Against Schedule</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Expected Wins</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>1st Place</t>
+  </si>
+  <si>
+    <t>2nd Place</t>
+  </si>
+  <si>
+    <t>3rd Place</t>
+  </si>
+  <si>
+    <t>4th Place</t>
+  </si>
+  <si>
+    <t>5th Place</t>
+  </si>
+  <si>
+    <t>6th Place</t>
+  </si>
+  <si>
+    <t>7th Place</t>
+  </si>
+  <si>
+    <t>8th Place</t>
+  </si>
+  <si>
+    <t>9th Place</t>
+  </si>
+  <si>
+    <t>Chance of Making Playoffs</t>
+  </si>
+  <si>
+    <t>Week_1</t>
+  </si>
+  <si>
+    <t>Week_2</t>
+  </si>
+  <si>
+    <t>Week_3</t>
+  </si>
+  <si>
+    <t>Week_4</t>
+  </si>
+  <si>
+    <t>Week_5</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Avg_Points_For</t>
+  </si>
+  <si>
+    <t>Team_Record</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Points_For</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Win_Pct</t>
+  </si>
+  <si>
+    <t>Avg_Opp_LPI</t>
+  </si>
+  <si>
+    <t>Games_Remaining</t>
+  </si>
+  <si>
+    <t>Ayush Chivate</t>
+  </si>
+  <si>
+    <t>Akshata Ketkar</t>
+  </si>
+  <si>
+    <t>Ritu Ketkar</t>
+  </si>
+  <si>
+    <t>Suhas Ketkar</t>
+  </si>
+  <si>
+    <t>Melissa Sefl</t>
+  </si>
+  <si>
+    <t>Ashutosh Ketkar</t>
+  </si>
+  <si>
+    <t>Vera Ketkar</t>
+  </si>
+  <si>
+    <t>Neel Ketkar</t>
+  </si>
+  <si>
+    <t>Dillan Ketkar</t>
   </si>
   <si>
     <t>1-2-0</t>
@@ -61,129 +190,6 @@
     <t>2-1-0</t>
   </si>
   <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>1-1-1</t>
-  </si>
-  <si>
-    <t>2-0-1</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Wins Against Schedule</t>
-  </si>
-  <si>
-    <t>Record</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Expected Wins</t>
-  </si>
-  <si>
-    <t>Difference</t>
-  </si>
-  <si>
-    <t>1st Place</t>
-  </si>
-  <si>
-    <t>2nd Place</t>
-  </si>
-  <si>
-    <t>3rd Place</t>
-  </si>
-  <si>
-    <t>4th Place</t>
-  </si>
-  <si>
-    <t>5th Place</t>
-  </si>
-  <si>
-    <t>6th Place</t>
-  </si>
-  <si>
-    <t>7th Place</t>
-  </si>
-  <si>
-    <t>8th Place</t>
-  </si>
-  <si>
-    <t>9th Place</t>
-  </si>
-  <si>
-    <t>Chance of Making Playoffs</t>
-  </si>
-  <si>
-    <t>Week_1</t>
-  </si>
-  <si>
-    <t>Week_2</t>
-  </si>
-  <si>
-    <t>Week_3</t>
-  </si>
-  <si>
-    <t>Week_4</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Avg_Points_For</t>
-  </si>
-  <si>
-    <t>Team_Record</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Points_For</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Win_Pct</t>
-  </si>
-  <si>
-    <t>Avg_Opp_LPI</t>
-  </si>
-  <si>
-    <t>Games_Remaining</t>
-  </si>
-  <si>
-    <t>Ritu Ketkar</t>
-  </si>
-  <si>
-    <t>Vera Ketkar</t>
-  </si>
-  <si>
-    <t>Akshata Ketkar</t>
-  </si>
-  <si>
-    <t>Ayush Chivate</t>
-  </si>
-  <si>
-    <t>Dillan Ketkar</t>
-  </si>
-  <si>
-    <t>Melissa Sefl</t>
-  </si>
-  <si>
-    <t>Neel Ketkar</t>
-  </si>
-  <si>
-    <t>Suhas Ketkar</t>
-  </si>
-  <si>
-    <t>Ashutosh Ketkar</t>
-  </si>
-  <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -208,69 +214,72 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
+    <t>3-1</t>
+  </si>
+  <si>
     <t>2-1</t>
   </si>
   <si>
-    <t>2-0</t>
+    <t>2-2</t>
   </si>
   <si>
     <t>1-2</t>
   </si>
   <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>11.4-2.5-0.1</t>
-  </si>
-  <si>
-    <t>9.5-4.3-0.2</t>
-  </si>
-  <si>
-    <t>9.3-4.6-0.1</t>
-  </si>
-  <si>
-    <t>8.9-4.9-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.2</t>
-  </si>
-  <si>
-    <t>5.9-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>4.1-9.7-0.1</t>
-  </si>
-  <si>
-    <t>12-3</t>
-  </si>
-  <si>
-    <t>10-6</t>
-  </si>
-  <si>
-    <t>9-5</t>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>11.1-2.9-0.1</t>
+  </si>
+  <si>
+    <t>10.5-3.3-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>8.1-5.7-0.1</t>
+  </si>
+  <si>
+    <t>7.7-6.2-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.8-0.1</t>
+  </si>
+  <si>
+    <t>3.9-10.0-0.1</t>
+  </si>
+  <si>
+    <t>11-4</t>
+  </si>
+  <si>
+    <t>11-5</t>
   </si>
   <si>
     <t>9-6</t>
   </si>
   <si>
-    <t>8-8</t>
-  </si>
-  <si>
-    <t>6-9</t>
+    <t>8-6</t>
+  </si>
+  <si>
+    <t>8-7</t>
+  </si>
+  <si>
+    <t>6-8</t>
   </si>
   <si>
     <t>5-10</t>
   </si>
   <si>
+    <t>5-9</t>
+  </si>
+  <si>
     <t>4-10</t>
   </si>
   <si>
@@ -286,27 +295,24 @@
     <t>↑6</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑3</t>
   </si>
   <si>
     <t>↓8</t>
   </si>
   <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -314,6 +320,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -761,31 +770,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>9</v>
-      </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -799,19 +808,19 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -825,31 +834,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -869,13 +878,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
@@ -904,10 +913,10 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
@@ -921,25 +930,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
@@ -953,28 +962,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
         <v>11</v>
@@ -991,25 +1000,25 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1019,30 +1028,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1121,6 +1130,32 @@
       </c>
       <c r="H4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1135,13 +1170,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1152,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1166,10 +1201,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1.222222222222222</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1180,10 +1215,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>1.333333333333333</v>
+        <v>1.444444444444444</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1194,10 +1229,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1.444444444444444</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1205,13 +1240,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1.444444444444444</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1222,10 +1257,10 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>1.555555555555556</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1233,13 +1268,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1.777777777777778</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1247,13 +1282,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1261,13 +1296,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>2.111111111111111</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1282,16 +1317,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1299,16 +1334,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2.444444444444445</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="D2">
-        <v>0.4444444444444446</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1316,16 +1351,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2.222222222222222</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="D3">
-        <v>0.2222222222222223</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1336,13 +1371,13 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>1.888888888888889</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D4">
-        <v>-0.1111111111111112</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1353,13 +1388,13 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1.666666666666667</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="D5">
-        <v>-0.3333333333333333</v>
+        <v>-0.8888888888888888</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1367,16 +1402,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1.444444444444444</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D6">
-        <v>0.4444444444444444</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1384,16 +1419,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>1.333333333333333</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="D7">
-        <v>1.333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1404,13 +1439,13 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>0.8888888888888888</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="D8">
-        <v>-0.1111111111111112</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1418,16 +1453,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.7777777777777778</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D9">
-        <v>-0.2222222222222222</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1435,16 +1470,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="C10">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="D10">
-        <v>-0.3333333333333334</v>
+        <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1459,37 +1494,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1497,19 +1532,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>77.2</v>
+        <v>54.9</v>
       </c>
       <c r="C2">
-        <v>17.1</v>
+        <v>35.4</v>
       </c>
       <c r="D2">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="E2">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1524,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1532,22 +1567,22 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>9.800000000000001</v>
+        <v>39.5</v>
       </c>
       <c r="C3">
-        <v>35.9</v>
+        <v>43.9</v>
       </c>
       <c r="D3">
-        <v>30.7</v>
+        <v>12.2</v>
       </c>
       <c r="E3">
-        <v>17.3</v>
+        <v>3.4</v>
       </c>
       <c r="F3">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="G3">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0.1</v>
@@ -1559,117 +1594,117 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>93.7</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>8.6</v>
+        <v>2.8</v>
       </c>
       <c r="C4">
-        <v>26.9</v>
+        <v>9.5</v>
       </c>
       <c r="D4">
-        <v>27.2</v>
+        <v>29.8</v>
       </c>
       <c r="E4">
-        <v>23.4</v>
+        <v>27.9</v>
       </c>
       <c r="F4">
-        <v>10.7</v>
+        <v>21.6</v>
       </c>
       <c r="G4">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>86.09999999999999</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="C5">
-        <v>16.4</v>
+        <v>6.8</v>
       </c>
       <c r="D5">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>28.7</v>
+        <v>31.5</v>
       </c>
       <c r="F5">
-        <v>17.2</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>4.9</v>
+        <v>7.9</v>
       </c>
       <c r="H5">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="I5">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
-        <v>76.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D6">
-        <v>8.6</v>
+        <v>19.3</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>24.6</v>
       </c>
       <c r="F6">
-        <v>41.9</v>
+        <v>30.4</v>
       </c>
       <c r="G6">
-        <v>15.3</v>
+        <v>12.9</v>
       </c>
       <c r="H6">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I6">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J6">
         <v>0.5</v>
       </c>
       <c r="K6">
-        <v>34.8</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1678,33 +1713,33 @@
         <v>0.1</v>
       </c>
       <c r="D7">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="E7">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="F7">
-        <v>13.4</v>
+        <v>14.3</v>
       </c>
       <c r="G7">
-        <v>41.1</v>
+        <v>33.6</v>
       </c>
       <c r="H7">
-        <v>22.5</v>
+        <v>25.5</v>
       </c>
       <c r="I7">
-        <v>10.4</v>
+        <v>13.1</v>
       </c>
       <c r="J7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K7">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1713,28 +1748,28 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E8">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="F8">
-        <v>8.300000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="G8">
-        <v>19.3</v>
+        <v>16.4</v>
       </c>
       <c r="H8">
-        <v>35.8</v>
+        <v>30.3</v>
       </c>
       <c r="I8">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="J8">
-        <v>11.1</v>
+        <v>17.9</v>
       </c>
       <c r="K8">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1745,31 +1780,31 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="F9">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="H9">
-        <v>17.9</v>
+        <v>24.3</v>
       </c>
       <c r="I9">
-        <v>30.9</v>
+        <v>32.3</v>
       </c>
       <c r="J9">
-        <v>38.6</v>
+        <v>16.7</v>
       </c>
       <c r="K9">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1786,25 +1821,25 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="H10">
-        <v>16.7</v>
+        <v>10.1</v>
       </c>
       <c r="I10">
-        <v>32.3</v>
+        <v>24.9</v>
       </c>
       <c r="J10">
-        <v>44.4</v>
+        <v>59.2</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1814,58 +1849,67 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="C2">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="D2">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E2">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>99.5</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>93.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="C3">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D3">
-        <v>92.80000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E3">
-        <v>93.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>98.3</v>
+      </c>
+      <c r="F3">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1876,98 +1920,116 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>92.30000000000001</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="E4">
-        <v>85.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>61.5</v>
+      </c>
+      <c r="F4">
+        <v>70.89999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>73.7</v>
+        <v>75.2</v>
       </c>
       <c r="C5">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="D5">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="E5">
-        <v>76.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>74.5</v>
+      </c>
+      <c r="F5">
+        <v>69.69999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>6.4</v>
+      </c>
+      <c r="C6">
+        <v>4.9</v>
+      </c>
+      <c r="D6">
+        <v>1.4</v>
+      </c>
+      <c r="E6">
+        <v>48</v>
+      </c>
+      <c r="F6">
+        <v>47.59999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>20.5</v>
-      </c>
-      <c r="C6">
-        <v>83.89999999999999</v>
-      </c>
-      <c r="D6">
-        <v>35</v>
-      </c>
-      <c r="E6">
-        <v>36.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B7">
-        <v>8.9</v>
+        <v>18.7</v>
       </c>
       <c r="C7">
-        <v>1.8</v>
+        <v>81.10000000000001</v>
       </c>
       <c r="D7">
-        <v>6.4</v>
+        <v>33.90000000000001</v>
       </c>
       <c r="E7">
-        <v>7.000000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>15.4</v>
+      </c>
+      <c r="F7">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0.4</v>
+      </c>
+      <c r="D8">
+        <v>0.4</v>
+      </c>
+      <c r="E8">
+        <v>1.7</v>
+      </c>
+      <c r="F8">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <v>7.8</v>
+      </c>
+      <c r="C9">
+        <v>2.4</v>
+      </c>
+      <c r="D9">
+        <v>5.5</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="B8">
-        <v>4.6</v>
-      </c>
-      <c r="C8">
-        <v>4.2</v>
-      </c>
-      <c r="D8">
-        <v>1.2</v>
-      </c>
-      <c r="E8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0.7000000000000001</v>
-      </c>
-      <c r="E9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -1982,6 +2044,9 @@
       </c>
       <c r="E10">
         <v>0.1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1996,28 +2061,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2025,28 +2090,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>154.49</v>
+        <v>140.55</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>143.97</v>
+        <v>142.4</v>
       </c>
       <c r="G2">
-        <v>0.545</v>
+        <v>0.517</v>
       </c>
       <c r="H2">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2054,28 +2119,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>207.77</v>
+        <v>148.39</v>
       </c>
       <c r="E3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3">
-        <v>142.27</v>
+        <v>140.14</v>
       </c>
       <c r="G3">
-        <v>0.545</v>
+        <v>0.442</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2083,28 +2148,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>152.34</v>
+        <v>139.65</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F4">
-        <v>139.36</v>
+        <v>143.15</v>
       </c>
       <c r="G4">
-        <v>0.455</v>
+        <v>0.517</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2112,28 +2177,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>135.7</v>
+        <v>159.21</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="F5">
-        <v>149.11</v>
+        <v>141.01</v>
       </c>
       <c r="G5">
-        <v>0.576</v>
+        <v>0.492</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2141,28 +2206,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>154.36</v>
+        <v>117.97</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>143.38</v>
+        <v>143.18</v>
       </c>
       <c r="G6">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2170,28 +2235,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>125.9</v>
+        <v>126.94</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>145.77</v>
+        <v>145.95</v>
       </c>
       <c r="G7">
-        <v>0.53</v>
+        <v>0.508</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2199,28 +2264,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>110.3</v>
+        <v>176.09</v>
       </c>
       <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8">
+        <v>141.04</v>
+      </c>
+      <c r="G8">
+        <v>0.517</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>10</v>
-      </c>
-      <c r="F8">
-        <v>142.96</v>
-      </c>
-      <c r="G8">
-        <v>0.5</v>
-      </c>
-      <c r="H8">
-        <v>-0.5</v>
-      </c>
-      <c r="I8">
-        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2228,28 +2293,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>123.4</v>
+        <v>126.67</v>
       </c>
       <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>144.27</v>
+      </c>
+      <c r="G9">
+        <v>0.475</v>
+      </c>
+      <c r="H9">
+        <v>-0.8</v>
+      </c>
+      <c r="I9">
         <v>10</v>
-      </c>
-      <c r="F9">
-        <v>139.14</v>
-      </c>
-      <c r="G9">
-        <v>0.485</v>
-      </c>
-      <c r="H9">
-        <v>-0.6</v>
-      </c>
-      <c r="I9">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2257,28 +2322,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>132.53</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>150.82</v>
+        <v>142.31</v>
       </c>
       <c r="G10">
-        <v>0.5610000000000001</v>
+        <v>0.475</v>
       </c>
       <c r="H10">
-        <v>-1.1</v>
+        <v>-1.5</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2293,31 +2358,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2325,28 +2390,28 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D2">
-        <v>154.36</v>
+        <v>148</v>
       </c>
       <c r="E2">
-        <v>463.08</v>
+        <v>592</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2354,173 +2419,173 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>135.7</v>
+        <v>140.55</v>
       </c>
       <c r="E3">
-        <v>407.1</v>
+        <v>562.2</v>
       </c>
       <c r="F3">
-        <v>93.7</v>
+        <v>99</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>138.5133333333333</v>
+        <v>126.94</v>
       </c>
       <c r="E4">
-        <v>415.54</v>
+        <v>507.76</v>
       </c>
       <c r="F4">
-        <v>86.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>132.5266666666667</v>
+        <v>132.065</v>
       </c>
       <c r="E5">
-        <v>397.58</v>
+        <v>528.26</v>
       </c>
       <c r="F5">
-        <v>76.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>123.4</v>
+        <v>126.67</v>
       </c>
       <c r="E6">
-        <v>370.2</v>
+        <v>506.6799999999999</v>
       </c>
       <c r="F6">
-        <v>34.8</v>
+        <v>49.1</v>
       </c>
       <c r="G6">
         <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>125.9</v>
+        <v>119.405</v>
       </c>
       <c r="E7">
-        <v>377.7</v>
+        <v>477.62</v>
       </c>
       <c r="F7">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="G7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>110.3</v>
+        <v>117.965</v>
       </c>
       <c r="E8">
-        <v>330.9</v>
+        <v>471.86</v>
       </c>
       <c r="F8">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="G8">
-        <v>11.1</v>
+        <v>17.9</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2528,28 +2593,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>101.56</v>
+        <v>111.29</v>
       </c>
       <c r="E9">
-        <v>304.68</v>
+        <v>445.16</v>
       </c>
       <c r="F9">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="G9">
-        <v>38.6</v>
+        <v>16.7</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2557,28 +2622,28 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>102.9933333333333</v>
+        <v>104.74</v>
       </c>
       <c r="E10">
-        <v>308.98</v>
+        <v>418.96</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10">
-        <v>44.4</v>
+        <v>59.2</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2593,19 +2658,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2613,19 +2678,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2633,19 +2698,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2656,16 +2721,16 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2673,10 +2738,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -2685,7 +2750,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2693,19 +2758,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2713,19 +2778,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2733,19 +2798,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2753,19 +2818,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2776,16 +2841,16 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D10">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2795,58 +2860,67 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>99</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>5</v>
       </c>
       <c r="D2">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>5</v>
       </c>
       <c r="D3">
+        <v>11</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="E3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2859,96 +2933,114 @@
       <c r="D4">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="C5">
         <v>-5</v>
       </c>
       <c r="D5">
+        <v>-7</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>-3</v>
+      </c>
+      <c r="C6">
+        <v>-3</v>
+      </c>
+      <c r="D6">
+        <v>-5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>-5</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>-1</v>
-      </c>
-      <c r="C6">
+      <c r="D8">
+        <v>-3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>-3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>-3</v>
-      </c>
-      <c r="C8">
-        <v>-3</v>
-      </c>
-      <c r="D8">
-        <v>-5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
       </c>
       <c r="B9">
         <v>-1</v>
       </c>
       <c r="C9">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>-7</v>
-      </c>
-      <c r="E9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>-8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -2961,8 +3053,11 @@
       <c r="D10">
         <v>-9</v>
       </c>
-      <c r="E10" t="s">
-        <v>93</v>
+      <c r="E10">
+        <v>-15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
+++ b/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="111">
   <si>
     <t>Lox, Stocks and 2 Skattebooms!</t>
   </si>
@@ -52,144 +52,153 @@
     <t>Walnut Rushers</t>
   </si>
   <si>
-    <t>0-4-0</t>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>3-1-1</t>
+  </si>
+  <si>
+    <t>2-2-1</t>
+  </si>
+  <si>
+    <t>1-3-1</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Wins Against Schedule</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Expected Wins</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>1st Place</t>
+  </si>
+  <si>
+    <t>2nd Place</t>
+  </si>
+  <si>
+    <t>3rd Place</t>
+  </si>
+  <si>
+    <t>4th Place</t>
+  </si>
+  <si>
+    <t>5th Place</t>
+  </si>
+  <si>
+    <t>6th Place</t>
+  </si>
+  <si>
+    <t>7th Place</t>
+  </si>
+  <si>
+    <t>8th Place</t>
+  </si>
+  <si>
+    <t>9th Place</t>
+  </si>
+  <si>
+    <t>Chance of Making Playoffs</t>
+  </si>
+  <si>
+    <t>Week_1</t>
+  </si>
+  <si>
+    <t>Week_2</t>
+  </si>
+  <si>
+    <t>Week_3</t>
+  </si>
+  <si>
+    <t>Week_4</t>
+  </si>
+  <si>
+    <t>Week_5</t>
+  </si>
+  <si>
+    <t>Week_6</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Avg_Points_For</t>
+  </si>
+  <si>
+    <t>Team_Record</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Points_For</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Win_Pct</t>
+  </si>
+  <si>
+    <t>Avg_Opp_LPI</t>
+  </si>
+  <si>
+    <t>Games_Remaining</t>
+  </si>
+  <si>
+    <t>Melissa Sefl</t>
+  </si>
+  <si>
+    <t>Neel Ketkar</t>
+  </si>
+  <si>
+    <t>Ashutosh Ketkar</t>
+  </si>
+  <si>
+    <t>Ayush Chivate</t>
+  </si>
+  <si>
+    <t>Ritu Ketkar</t>
+  </si>
+  <si>
+    <t>Suhas Ketkar</t>
+  </si>
+  <si>
+    <t>Dillan Ketkar</t>
+  </si>
+  <si>
+    <t>Akshata Ketkar</t>
+  </si>
+  <si>
+    <t>Vera Ketkar</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
   </si>
   <si>
     <t>1-3-0</t>
   </si>
   <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>1-2-1</t>
-  </si>
-  <si>
-    <t>2-1-1</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Wins Against Schedule</t>
-  </si>
-  <si>
-    <t>Record</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Expected Wins</t>
-  </si>
-  <si>
-    <t>Difference</t>
-  </si>
-  <si>
-    <t>1st Place</t>
-  </si>
-  <si>
-    <t>2nd Place</t>
-  </si>
-  <si>
-    <t>3rd Place</t>
-  </si>
-  <si>
-    <t>4th Place</t>
-  </si>
-  <si>
-    <t>5th Place</t>
-  </si>
-  <si>
-    <t>6th Place</t>
-  </si>
-  <si>
-    <t>7th Place</t>
-  </si>
-  <si>
-    <t>8th Place</t>
-  </si>
-  <si>
-    <t>9th Place</t>
-  </si>
-  <si>
-    <t>Chance of Making Playoffs</t>
-  </si>
-  <si>
-    <t>Week_1</t>
-  </si>
-  <si>
-    <t>Week_2</t>
-  </si>
-  <si>
-    <t>Week_3</t>
-  </si>
-  <si>
-    <t>Week_4</t>
-  </si>
-  <si>
-    <t>Week_5</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Avg_Points_For</t>
-  </si>
-  <si>
-    <t>Team_Record</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Points_For</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Win_Pct</t>
-  </si>
-  <si>
-    <t>Avg_Opp_LPI</t>
-  </si>
-  <si>
-    <t>Games_Remaining</t>
-  </si>
-  <si>
-    <t>Ayush Chivate</t>
-  </si>
-  <si>
-    <t>Akshata Ketkar</t>
-  </si>
-  <si>
-    <t>Ritu Ketkar</t>
-  </si>
-  <si>
-    <t>Suhas Ketkar</t>
-  </si>
-  <si>
-    <t>Melissa Sefl</t>
-  </si>
-  <si>
-    <t>Ashutosh Ketkar</t>
-  </si>
-  <si>
-    <t>Vera Ketkar</t>
-  </si>
-  <si>
-    <t>Neel Ketkar</t>
-  </si>
-  <si>
-    <t>Dillan Ketkar</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -214,72 +223,66 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
+    <t>3-2</t>
+  </si>
+  <si>
     <t>3-1</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
     <t>2-2</t>
   </si>
   <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>11.1-2.9-0.1</t>
-  </si>
-  <si>
-    <t>10.5-3.3-0.1</t>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>10.0-3.9-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.7-0.1</t>
   </si>
   <si>
     <t>8.6-5.3-0.1</t>
   </si>
   <si>
-    <t>8.1-5.7-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.8-0.1</t>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.9-0.1</t>
   </si>
   <si>
     <t>3.9-10.0-0.1</t>
   </si>
   <si>
-    <t>11-4</t>
-  </si>
-  <si>
-    <t>11-5</t>
+    <t>10-5</t>
+  </si>
+  <si>
+    <t>9-5</t>
   </si>
   <si>
     <t>9-6</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
     <t>8-7</t>
   </si>
   <si>
     <t>6-8</t>
   </si>
   <si>
+    <t>5-9</t>
+  </si>
+  <si>
     <t>5-10</t>
   </si>
   <si>
-    <t>5-9</t>
-  </si>
-  <si>
     <t>4-10</t>
   </si>
   <si>
@@ -295,22 +298,28 @@
     <t>↑6</t>
   </si>
   <si>
+    <t>↑4</t>
+  </si>
+  <si>
     <t>↓6</t>
   </si>
   <si>
-    <t>↓2</t>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓8</t>
   </si>
   <si>
     <t>↑10</t>
   </si>
   <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓8</t>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓10</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -323,6 +332,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -741,28 +753,28 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -788,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
         <v>10</v>
@@ -808,25 +820,25 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -837,28 +849,28 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
         <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -878,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -901,28 +913,28 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -942,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
@@ -962,31 +974,31 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
       <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1006,19 +1018,19 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1028,30 +1040,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1059,19 +1071,19 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>14</v>
@@ -1088,22 +1100,22 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>-9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1114,22 +1126,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>-5</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1137,24 +1149,50 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>-5</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1170,13 +1208,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1187,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.8888888888888888</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -1201,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1.444444444444444</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -1215,10 +1253,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>1.444444444444444</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1226,13 +1264,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>2.111111111111111</v>
+        <v>2.444444444444445</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1240,13 +1278,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2.222222222222222</v>
+        <v>2.444444444444445</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1254,13 +1292,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>2.222222222222222</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1268,10 +1306,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>2.222222222222222</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1282,13 +1320,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>2.333333333333333</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1299,10 +1337,10 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>2.888888888888889</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1317,16 +1355,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1334,16 +1372,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>3.111111111111111</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="D2">
-        <v>0.1111111111111112</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1351,16 +1389,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.111111111111111</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D3">
-        <v>0.1111111111111112</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1371,13 +1409,13 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>2.333333333333333</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>0.3333333333333335</v>
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1385,16 +1423,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>2.111111111111111</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="D5">
-        <v>-0.8888888888888888</v>
+        <v>-0.4444444444444446</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1402,13 +1440,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>1.666666666666667</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="D6">
-        <v>-0.3333333333333333</v>
+        <v>-0.4444444444444446</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -1419,16 +1457,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>1.555555555555556</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1436,16 +1474,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1.555555555555556</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="D8">
-        <v>0.5555555555555556</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1456,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.333333333333333</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="D9">
-        <v>1.333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1470,16 +1508,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1494,37 +1532,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1532,22 +1570,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>54.9</v>
+        <v>58.6</v>
       </c>
       <c r="C2">
-        <v>35.4</v>
+        <v>24.2</v>
       </c>
       <c r="D2">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1559,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>99.7</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1567,69 +1605,69 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>39.5</v>
+        <v>17.2</v>
       </c>
       <c r="C3">
-        <v>43.9</v>
+        <v>29.2</v>
       </c>
       <c r="D3">
-        <v>12.2</v>
+        <v>25.7</v>
       </c>
       <c r="E3">
-        <v>3.4</v>
+        <v>15.6</v>
       </c>
       <c r="F3">
-        <v>0.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
+        <v>0.3</v>
+      </c>
+      <c r="I3">
         <v>0.1</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
-        <v>99</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
-        <v>2.8</v>
+        <v>10.3</v>
       </c>
       <c r="C4">
-        <v>9.5</v>
+        <v>18.1</v>
       </c>
       <c r="D4">
-        <v>29.8</v>
+        <v>26.3</v>
       </c>
       <c r="E4">
-        <v>27.9</v>
+        <v>21.3</v>
       </c>
       <c r="F4">
-        <v>21.6</v>
+        <v>17.1</v>
       </c>
       <c r="G4">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K4">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1637,179 +1675,179 @@
         <v>8</v>
       </c>
       <c r="B5">
+        <v>9.9</v>
+      </c>
+      <c r="C5">
+        <v>18.4</v>
+      </c>
+      <c r="D5">
+        <v>20.4</v>
+      </c>
+      <c r="E5">
+        <v>24.2</v>
+      </c>
+      <c r="F5">
+        <v>19.2</v>
+      </c>
+      <c r="G5">
+        <v>5.6</v>
+      </c>
+      <c r="H5">
         <v>1.8</v>
       </c>
-      <c r="C5">
-        <v>6.8</v>
-      </c>
-      <c r="D5">
-        <v>29</v>
-      </c>
-      <c r="E5">
-        <v>31.5</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5">
-        <v>7.9</v>
-      </c>
-      <c r="H5">
-        <v>1.9</v>
-      </c>
       <c r="I5">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>69.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="D6">
-        <v>19.3</v>
+        <v>16.2</v>
       </c>
       <c r="E6">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="F6">
-        <v>30.4</v>
+        <v>29.3</v>
       </c>
       <c r="G6">
-        <v>12.9</v>
+        <v>10.4</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="I6">
         <v>1.3</v>
       </c>
       <c r="J6">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="K6">
-        <v>49.1</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="D7">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E7">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="F7">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
       <c r="G7">
-        <v>33.6</v>
+        <v>29.9</v>
       </c>
       <c r="H7">
-        <v>25.5</v>
+        <v>26.4</v>
       </c>
       <c r="I7">
-        <v>13.1</v>
+        <v>18.3</v>
       </c>
       <c r="J7">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="K7">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E8">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>16.4</v>
+        <v>24.4</v>
       </c>
       <c r="H8">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="I8">
-        <v>26.9</v>
+        <v>25.2</v>
       </c>
       <c r="J8">
-        <v>17.9</v>
+        <v>11.7</v>
       </c>
       <c r="K8">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="F9">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>18.8</v>
+        <v>19.6</v>
       </c>
       <c r="H9">
-        <v>24.3</v>
+        <v>28.4</v>
       </c>
       <c r="I9">
-        <v>32.3</v>
+        <v>31.5</v>
       </c>
       <c r="J9">
-        <v>16.7</v>
+        <v>14.5</v>
       </c>
       <c r="K9">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1821,25 +1859,25 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="H10">
-        <v>10.1</v>
+        <v>7.1</v>
       </c>
       <c r="I10">
-        <v>24.9</v>
+        <v>22.5</v>
       </c>
       <c r="J10">
-        <v>59.2</v>
+        <v>67.2</v>
       </c>
       <c r="K10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1849,203 +1887,233 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>99.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C2">
-        <v>96.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D2">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E2">
-        <v>99.5</v>
+        <v>99.7</v>
       </c>
       <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>98</v>
+      </c>
+      <c r="G2">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3">
+        <v>93.8</v>
+      </c>
+      <c r="C3">
+        <v>99.5</v>
+      </c>
+      <c r="D3">
         <v>92.90000000000001</v>
       </c>
-      <c r="C3">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="D3">
-        <v>92.40000000000001</v>
-      </c>
       <c r="E3">
-        <v>98.3</v>
+        <v>98</v>
       </c>
       <c r="F3">
-        <v>99.40000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="G3">
+        <v>87.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4">
+        <v>99.7</v>
+      </c>
+      <c r="C4">
         <v>99.90000000000001</v>
       </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
       <c r="D4">
-        <v>92.10000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="E4">
-        <v>61.5</v>
+        <v>60.5</v>
       </c>
       <c r="F4">
-        <v>70.89999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>72.7</v>
+      </c>
+      <c r="G4">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4.9</v>
+      </c>
+      <c r="C5">
+        <v>3.5</v>
+      </c>
+      <c r="D5">
+        <v>1.4</v>
+      </c>
+      <c r="E5">
+        <v>48</v>
+      </c>
+      <c r="F5">
+        <v>76</v>
+      </c>
+      <c r="G5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5">
-        <v>75.2</v>
-      </c>
-      <c r="C5">
-        <v>15.3</v>
-      </c>
-      <c r="D5">
-        <v>74.2</v>
-      </c>
-      <c r="E5">
-        <v>74.5</v>
-      </c>
-      <c r="F5">
-        <v>69.69999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B6">
-        <v>6.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C6">
-        <v>4.9</v>
+        <v>18.6</v>
       </c>
       <c r="D6">
-        <v>1.4</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E6">
-        <v>48</v>
+        <v>75.7</v>
       </c>
       <c r="F6">
-        <v>47.59999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>51.8</v>
+      </c>
+      <c r="G6">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>0.1</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0.2</v>
+      </c>
+      <c r="F7">
+        <v>4.3</v>
+      </c>
+      <c r="G7">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>18.7</v>
-      </c>
-      <c r="C7">
+      <c r="B8">
+        <v>19</v>
+      </c>
+      <c r="C8">
         <v>81.10000000000001</v>
       </c>
-      <c r="D7">
-        <v>33.90000000000001</v>
-      </c>
-      <c r="E7">
-        <v>15.4</v>
-      </c>
-      <c r="F7">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0.4</v>
-      </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>32.8</v>
       </c>
       <c r="E8">
-        <v>1.7</v>
+        <v>14.7</v>
       </c>
       <c r="F8">
         <v>2.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B9">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C9">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>5.5</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F9">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>1.7</v>
+      </c>
+      <c r="G9">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D10">
         <v>0.2</v>
       </c>
       <c r="E10">
+        <v>1.9</v>
+      </c>
+      <c r="F10">
         <v>0.1</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0</v>
       </c>
     </row>
@@ -2061,28 +2129,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2090,28 +2158,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>140.55</v>
+        <v>118.18</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>142.4</v>
+        <v>143.31</v>
       </c>
       <c r="G2">
-        <v>0.517</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2119,28 +2187,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>148.39</v>
+        <v>133.27</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>140.14</v>
+        <v>143.31</v>
       </c>
       <c r="G3">
-        <v>0.442</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2148,28 +2216,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>139.65</v>
+        <v>127.3</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>143.15</v>
+        <v>143.31</v>
       </c>
       <c r="G4">
-        <v>0.517</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2177,28 +2245,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>159.21</v>
+        <v>171.21</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5">
-        <v>141.01</v>
+        <v>143.31</v>
       </c>
       <c r="G5">
-        <v>0.492</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2206,28 +2274,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>117.97</v>
+        <v>145.48</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="F6">
-        <v>143.18</v>
+        <v>143.31</v>
       </c>
       <c r="G6">
-        <v>0.475</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2235,28 +2303,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>126.94</v>
+        <v>150.6</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>145.95</v>
+        <v>143.31</v>
       </c>
       <c r="G7">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2264,28 +2332,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>176.09</v>
+        <v>146.89</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>141.04</v>
+        <v>143.31</v>
       </c>
       <c r="G8">
-        <v>0.517</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2293,28 +2361,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>126.67</v>
+        <v>130.56</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F9">
-        <v>144.27</v>
+        <v>143.31</v>
       </c>
       <c r="G9">
-        <v>0.475</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2322,28 +2390,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>148</v>
+        <v>166.29</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="F10">
-        <v>142.31</v>
+        <v>143.31</v>
       </c>
       <c r="G10">
-        <v>0.475</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2358,31 +2426,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2390,28 +2458,28 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D2">
-        <v>148</v>
+        <v>146.892</v>
       </c>
       <c r="E2">
-        <v>592</v>
+        <v>734.46</v>
       </c>
       <c r="F2">
-        <v>99.7</v>
+        <v>97.89999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2419,57 +2487,57 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C3">
         <v>0.75</v>
       </c>
       <c r="D3">
-        <v>140.55</v>
+        <v>136.964</v>
       </c>
       <c r="E3">
-        <v>562.2</v>
+        <v>684.8200000000001</v>
       </c>
       <c r="F3">
-        <v>99</v>
+        <v>87.7</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>126.94</v>
+        <v>133.268</v>
       </c>
       <c r="E4">
-        <v>507.76</v>
+        <v>666.3399999999999</v>
       </c>
       <c r="F4">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2477,25 +2545,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
-        <v>132.065</v>
+        <v>133.032</v>
       </c>
       <c r="E5">
-        <v>528.26</v>
+        <v>665.16</v>
       </c>
       <c r="F5">
-        <v>69.09999999999999</v>
+        <v>72.89999999999999</v>
       </c>
       <c r="G5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
         <v>80</v>
@@ -2503,147 +2571,147 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>126.67</v>
+        <v>127.3</v>
       </c>
       <c r="E6">
-        <v>506.6799999999999</v>
+        <v>636.5</v>
       </c>
       <c r="F6">
-        <v>49.1</v>
+        <v>54.90000000000001</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>119.405</v>
+        <v>116.38</v>
       </c>
       <c r="E7">
-        <v>477.62</v>
+        <v>581.9000000000001</v>
       </c>
       <c r="F7">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
       <c r="G7">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D8">
-        <v>117.965</v>
+        <v>120.484</v>
       </c>
       <c r="E8">
-        <v>471.86</v>
+        <v>602.42</v>
       </c>
       <c r="F8">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G8">
-        <v>17.9</v>
+        <v>11.7</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>111.29</v>
+        <v>118.176</v>
       </c>
       <c r="E9">
-        <v>445.16</v>
+        <v>590.88</v>
       </c>
       <c r="F9">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>16.7</v>
+        <v>14.5</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>104.74</v>
+        <v>104.444</v>
       </c>
       <c r="E10">
-        <v>418.96</v>
+        <v>522.22</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>59.2</v>
+        <v>67.2</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2658,19 +2726,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2678,19 +2746,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2698,19 +2766,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2718,19 +2786,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2738,19 +2806,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2758,19 +2826,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2778,19 +2846,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2798,19 +2866,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
         <v>50</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2821,16 +2889,16 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2838,19 +2906,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2860,167 +2928,191 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>103</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="C3">
+        <v>-5</v>
+      </c>
+      <c r="D3">
+        <v>-7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
         <v>5</v>
-      </c>
-      <c r="D3">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
       </c>
       <c r="D4">
         <v>5</v>
       </c>
       <c r="E4">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>-3</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
+      <c r="G5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>-1</v>
-      </c>
-      <c r="C5">
+      <c r="C6">
         <v>-5</v>
       </c>
-      <c r="D5">
-        <v>-7</v>
-      </c>
-      <c r="E5">
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="F5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7">
         <v>-3</v>
       </c>
-      <c r="C6">
-        <v>-3</v>
-      </c>
-      <c r="D6">
+      <c r="G7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>-8</v>
+      </c>
+      <c r="C8">
+        <v>-12</v>
+      </c>
+      <c r="D8">
+        <v>-9</v>
+      </c>
+      <c r="E8">
+        <v>-15</v>
+      </c>
+      <c r="F8">
         <v>-5</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>-5</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>-3</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
@@ -3036,28 +3128,34 @@
       <c r="E9">
         <v>-8</v>
       </c>
-      <c r="F9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9">
+        <v>-7</v>
+      </c>
+      <c r="G9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="C10">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="D10">
+        <v>-5</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>-9</v>
       </c>
-      <c r="E10">
-        <v>-15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>90</v>
+      <c r="G10" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
+++ b/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="116">
   <si>
     <t>Lox, Stocks and 2 Skattebooms!</t>
   </si>
@@ -52,7 +52,148 @@
     <t>Walnut Rushers</t>
   </si>
   <si>
-    <t>1-4-0</t>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>3-2-1</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>2-3-1</t>
+  </si>
+  <si>
+    <t>4-1-1</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Wins Against Schedule</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Expected Wins</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>1st Place</t>
+  </si>
+  <si>
+    <t>2nd Place</t>
+  </si>
+  <si>
+    <t>3rd Place</t>
+  </si>
+  <si>
+    <t>4th Place</t>
+  </si>
+  <si>
+    <t>5th Place</t>
+  </si>
+  <si>
+    <t>6th Place</t>
+  </si>
+  <si>
+    <t>7th Place</t>
+  </si>
+  <si>
+    <t>8th Place</t>
+  </si>
+  <si>
+    <t>9th Place</t>
+  </si>
+  <si>
+    <t>Chance of Making Playoffs</t>
+  </si>
+  <si>
+    <t>Week_1</t>
+  </si>
+  <si>
+    <t>Week_2</t>
+  </si>
+  <si>
+    <t>Week_3</t>
+  </si>
+  <si>
+    <t>Week_4</t>
+  </si>
+  <si>
+    <t>Week_5</t>
+  </si>
+  <si>
+    <t>Week_6</t>
+  </si>
+  <si>
+    <t>Week_7</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Avg_Points_For</t>
+  </si>
+  <si>
+    <t>Team_Record</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Points_For</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Win_Pct</t>
+  </si>
+  <si>
+    <t>Avg_Opp_LPI</t>
+  </si>
+  <si>
+    <t>Games_Remaining</t>
+  </si>
+  <si>
+    <t>Melissa Sefl</t>
+  </si>
+  <si>
+    <t>Suhas Ketkar</t>
+  </si>
+  <si>
+    <t>Ritu Ketkar</t>
+  </si>
+  <si>
+    <t>Ayush Chivate</t>
+  </si>
+  <si>
+    <t>Akshata Ketkar</t>
+  </si>
+  <si>
+    <t>Ashutosh Ketkar</t>
+  </si>
+  <si>
+    <t>Dillan Ketkar</t>
+  </si>
+  <si>
+    <t>Vera Ketkar</t>
+  </si>
+  <si>
+    <t>Neel Ketkar</t>
   </si>
   <si>
     <t>2-3-0</t>
@@ -64,141 +205,6 @@
     <t>4-1-0</t>
   </si>
   <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>3-1-1</t>
-  </si>
-  <si>
-    <t>2-2-1</t>
-  </si>
-  <si>
-    <t>1-3-1</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Wins Against Schedule</t>
-  </si>
-  <si>
-    <t>Record</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Expected Wins</t>
-  </si>
-  <si>
-    <t>Difference</t>
-  </si>
-  <si>
-    <t>1st Place</t>
-  </si>
-  <si>
-    <t>2nd Place</t>
-  </si>
-  <si>
-    <t>3rd Place</t>
-  </si>
-  <si>
-    <t>4th Place</t>
-  </si>
-  <si>
-    <t>5th Place</t>
-  </si>
-  <si>
-    <t>6th Place</t>
-  </si>
-  <si>
-    <t>7th Place</t>
-  </si>
-  <si>
-    <t>8th Place</t>
-  </si>
-  <si>
-    <t>9th Place</t>
-  </si>
-  <si>
-    <t>Chance of Making Playoffs</t>
-  </si>
-  <si>
-    <t>Week_1</t>
-  </si>
-  <si>
-    <t>Week_2</t>
-  </si>
-  <si>
-    <t>Week_3</t>
-  </si>
-  <si>
-    <t>Week_4</t>
-  </si>
-  <si>
-    <t>Week_5</t>
-  </si>
-  <si>
-    <t>Week_6</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Avg_Points_For</t>
-  </si>
-  <si>
-    <t>Team_Record</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Points_For</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Win_Pct</t>
-  </si>
-  <si>
-    <t>Avg_Opp_LPI</t>
-  </si>
-  <si>
-    <t>Games_Remaining</t>
-  </si>
-  <si>
-    <t>Melissa Sefl</t>
-  </si>
-  <si>
-    <t>Neel Ketkar</t>
-  </si>
-  <si>
-    <t>Ashutosh Ketkar</t>
-  </si>
-  <si>
-    <t>Ayush Chivate</t>
-  </si>
-  <si>
-    <t>Ritu Ketkar</t>
-  </si>
-  <si>
-    <t>Suhas Ketkar</t>
-  </si>
-  <si>
-    <t>Dillan Ketkar</t>
-  </si>
-  <si>
-    <t>Akshata Ketkar</t>
-  </si>
-  <si>
-    <t>Vera Ketkar</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -223,55 +229,61 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
     <t>3-2</t>
   </si>
   <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>10.0-3.9-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.7-0.1</t>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.1</t>
+  </si>
+  <si>
+    <t>9.6-4.3-0.1</t>
   </si>
   <si>
     <t>8.6-5.3-0.1</t>
   </si>
   <si>
-    <t>8.1-5.8-0.1</t>
-  </si>
-  <si>
-    <t>6.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.9-0.1</t>
-  </si>
-  <si>
-    <t>3.9-10.0-0.1</t>
-  </si>
-  <si>
-    <t>10-5</t>
-  </si>
-  <si>
-    <t>9-5</t>
+    <t>8.2-5.7-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>5.6-8.3-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.4-0.1</t>
+  </si>
+  <si>
+    <t>4.7-9.2-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
   </si>
   <si>
     <t>9-6</t>
   </si>
   <si>
-    <t>8-7</t>
+    <t>10-4</t>
+  </si>
+  <si>
+    <t>8-6</t>
+  </si>
+  <si>
+    <t>8-5</t>
   </si>
   <si>
     <t>6-8</t>
@@ -280,12 +292,12 @@
     <t>5-9</t>
   </si>
   <si>
+    <t>4-10</t>
+  </si>
+  <si>
     <t>5-10</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -295,33 +307,33 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
     <t>↑6</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓10</t>
   </si>
   <si>
     <t>↓8</t>
   </si>
   <si>
-    <t>↑10</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓10</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -335,6 +347,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -759,22 +774,22 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -785,7 +800,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -800,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
         <v>10</v>
@@ -826,19 +841,19 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
         <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -849,28 +864,28 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
         <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -878,28 +893,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
       </c>
       <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
         <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>10</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
@@ -910,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
@@ -919,22 +934,22 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>16</v>
       </c>
       <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
         <v>12</v>
       </c>
-      <c r="I7" t="s">
-        <v>10</v>
-      </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -945,28 +960,28 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
       </c>
       <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -974,7 +989,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
@@ -986,13 +1001,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
         <v>16</v>
@@ -1012,7 +1027,7 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -1030,7 +1045,7 @@
         <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1040,30 +1055,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1175,25 +1190,129 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="E6">
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>-3</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
         <v>5</v>
       </c>
-      <c r="F6">
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="G6">
+      <c r="G8">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H8" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>-13</v>
+      </c>
+      <c r="F9">
+        <v>-15</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <v>-3</v>
+      </c>
+      <c r="F10">
+        <v>-4</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1208,13 +1327,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1222,13 +1341,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1.777777777777778</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1236,13 +1355,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1253,7 +1372,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>2.333333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -1267,10 +1386,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>2.444444444444445</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1278,13 +1397,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>2.444444444444445</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1295,7 +1414,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>2.555555555555555</v>
+        <v>3.222222222222222</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -1309,10 +1428,10 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>2.777777777777778</v>
+        <v>3.222222222222222</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1320,13 +1439,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>2.888888888888889</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1334,13 +1453,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1355,16 +1474,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1375,13 +1494,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>3.777777777777778</v>
+        <v>4.222222222222222</v>
       </c>
       <c r="D2">
-        <v>0.7777777777777777</v>
+        <v>1.222222222222222</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1389,16 +1508,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>3.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>0.3333333333333335</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1406,16 +1525,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.555555555555555</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>0.5555555555555554</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1426,13 +1545,13 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>2.555555555555555</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D5">
-        <v>-0.4444444444444446</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1443,10 +1562,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>2.555555555555555</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>-0.4444444444444446</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -1460,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.555555555555555</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.5555555555555554</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1474,13 +1593,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>1.888888888888889</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="D8">
-        <v>0.8888888888888888</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
@@ -1491,16 +1610,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>1.555555555555556</v>
+        <v>2.111111111111111</v>
       </c>
       <c r="D9">
-        <v>0.5555555555555556</v>
+        <v>0.1111111111111112</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1508,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>1.555555555555556</v>
@@ -1517,7 +1636,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1532,37 +1651,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1570,25 +1689,25 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>58.6</v>
+        <v>34.5</v>
       </c>
       <c r="C2">
-        <v>24.2</v>
+        <v>30.3</v>
       </c>
       <c r="D2">
-        <v>9.6</v>
+        <v>18.5</v>
       </c>
       <c r="E2">
-        <v>5.5</v>
+        <v>12.1</v>
       </c>
       <c r="F2">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="G2">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1597,222 +1716,222 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>97.90000000000001</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>17.2</v>
+        <v>41.2</v>
       </c>
       <c r="C3">
         <v>29.2</v>
       </c>
       <c r="D3">
-        <v>25.7</v>
+        <v>15.2</v>
       </c>
       <c r="E3">
-        <v>15.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F3">
-        <v>9.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="H3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>87.7</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="C4">
-        <v>18.1</v>
+        <v>16.5</v>
       </c>
       <c r="D4">
-        <v>26.3</v>
+        <v>23.5</v>
       </c>
       <c r="E4">
-        <v>21.3</v>
+        <v>27.9</v>
       </c>
       <c r="F4">
-        <v>17.1</v>
+        <v>18.4</v>
       </c>
       <c r="G4">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J4">
         <v>0.1</v>
       </c>
       <c r="K4">
-        <v>76</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="C5">
-        <v>18.4</v>
+        <v>14.1</v>
       </c>
       <c r="D5">
-        <v>20.4</v>
+        <v>24.4</v>
       </c>
       <c r="E5">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="F5">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="G5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="C6">
         <v>9.4</v>
       </c>
       <c r="D6">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="E6">
-        <v>25.3</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>29.3</v>
+        <v>29.7</v>
       </c>
       <c r="G6">
-        <v>10.4</v>
+        <v>12.6</v>
       </c>
       <c r="H6">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J6">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K6">
-        <v>54.9</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="D7">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>13.1</v>
+        <v>11.2</v>
       </c>
       <c r="G7">
-        <v>29.9</v>
+        <v>27.8</v>
       </c>
       <c r="H7">
-        <v>26.4</v>
+        <v>29.6</v>
       </c>
       <c r="I7">
-        <v>18.3</v>
+        <v>17.2</v>
       </c>
       <c r="J7">
-        <v>6.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K7">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
         <v>0.4</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G8">
-        <v>24.4</v>
+        <v>28.8</v>
       </c>
       <c r="H8">
-        <v>30.2</v>
+        <v>27</v>
       </c>
       <c r="I8">
-        <v>25.2</v>
+        <v>20.2</v>
       </c>
       <c r="J8">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="K8">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1821,33 +1940,33 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E9">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="G9">
-        <v>19.6</v>
+        <v>8.6</v>
       </c>
       <c r="H9">
-        <v>28.4</v>
+        <v>16</v>
       </c>
       <c r="I9">
-        <v>31.5</v>
+        <v>29.1</v>
       </c>
       <c r="J9">
-        <v>14.5</v>
+        <v>42.9</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1856,28 +1975,28 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
+        <v>2.4</v>
+      </c>
+      <c r="G10">
+        <v>11.2</v>
+      </c>
+      <c r="H10">
+        <v>19.4</v>
+      </c>
+      <c r="I10">
+        <v>31.6</v>
+      </c>
+      <c r="J10">
+        <v>34.9</v>
+      </c>
+      <c r="K10">
         <v>0.5</v>
-      </c>
-      <c r="G10">
-        <v>2.7</v>
-      </c>
-      <c r="H10">
-        <v>7.1</v>
-      </c>
-      <c r="I10">
-        <v>22.5</v>
-      </c>
-      <c r="J10">
-        <v>67.2</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1887,214 +2006,241 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>39</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>93.10000000000001</v>
+      </c>
+      <c r="E2">
+        <v>57.9</v>
+      </c>
+      <c r="F2">
+        <v>73.8</v>
+      </c>
+      <c r="G2">
+        <v>93</v>
+      </c>
+      <c r="H2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
+      <c r="B3">
+        <v>99.7</v>
+      </c>
+      <c r="C3">
+        <v>96.2</v>
+      </c>
+      <c r="D3">
+        <v>99.7</v>
+      </c>
+      <c r="E3">
+        <v>99.8</v>
+      </c>
+      <c r="F3">
+        <v>97</v>
+      </c>
+      <c r="G3">
+        <v>91.10000000000001</v>
+      </c>
+      <c r="H3">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>92.80000000000001</v>
+      </c>
+      <c r="C4">
         <v>99.59999999999999</v>
       </c>
-      <c r="C2">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="D2">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E2">
-        <v>99.7</v>
-      </c>
-      <c r="F2">
-        <v>98</v>
-      </c>
-      <c r="G2">
-        <v>97.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>93.8</v>
-      </c>
-      <c r="C3">
-        <v>99.5</v>
-      </c>
-      <c r="D3">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="E3">
-        <v>98</v>
-      </c>
-      <c r="F3">
-        <v>92.80000000000001</v>
-      </c>
-      <c r="G3">
-        <v>87.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="D4">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="E4">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F4">
+        <v>92.7</v>
+      </c>
+      <c r="G4">
+        <v>71.8</v>
+      </c>
+      <c r="H4">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="C5">
+        <v>13.9</v>
+      </c>
+      <c r="D5">
+        <v>72</v>
+      </c>
+      <c r="E5">
+        <v>70.5</v>
+      </c>
+      <c r="F5">
+        <v>50.5</v>
+      </c>
+      <c r="G5">
+        <v>66.5</v>
+      </c>
+      <c r="H5">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5.2</v>
+      </c>
+      <c r="C6">
+        <v>3.6</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>52.5</v>
+      </c>
+      <c r="F6">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G6">
+        <v>67.10000000000001</v>
+      </c>
+      <c r="H6">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>21.2</v>
+      </c>
+      <c r="C7">
+        <v>84</v>
+      </c>
+      <c r="D7">
+        <v>35.5</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>3.3</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0.1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>4.2</v>
+      </c>
+      <c r="G8">
+        <v>3.9</v>
+      </c>
+      <c r="H8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>99.7</v>
-      </c>
-      <c r="C4">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D4">
-        <v>91.5</v>
-      </c>
-      <c r="E4">
-        <v>60.5</v>
-      </c>
-      <c r="F4">
-        <v>72.7</v>
-      </c>
-      <c r="G4">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4.9</v>
-      </c>
-      <c r="C5">
-        <v>3.5</v>
-      </c>
-      <c r="D5">
-        <v>1.4</v>
-      </c>
-      <c r="E5">
-        <v>48</v>
-      </c>
-      <c r="F5">
-        <v>76</v>
-      </c>
-      <c r="G5">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="C6">
-        <v>18.6</v>
-      </c>
-      <c r="D6">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="E6">
-        <v>75.7</v>
-      </c>
-      <c r="F6">
-        <v>51.8</v>
-      </c>
-      <c r="G6">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>0.1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0.2</v>
-      </c>
-      <c r="F7">
-        <v>4.3</v>
-      </c>
-      <c r="G7">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>81.10000000000001</v>
-      </c>
-      <c r="D8">
-        <v>32.8</v>
-      </c>
-      <c r="E8">
-        <v>14.7</v>
-      </c>
-      <c r="F8">
-        <v>2.6</v>
-      </c>
-      <c r="G8">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9">
-        <v>9.800000000000001</v>
-      </c>
       <c r="C9">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D9">
-        <v>7.000000000000001</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="E9">
         <v>1.3</v>
       </c>
       <c r="F9">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="G9">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="H9">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2102,19 +2248,22 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E10">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="H10">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -2129,28 +2278,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2161,25 +2310,25 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>118.18</v>
+        <v>113.93</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>143.31</v>
+        <v>139.78</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.517</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2187,28 +2336,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>133.27</v>
+        <v>140.03</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F3">
-        <v>143.31</v>
+        <v>143.04</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.546</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2216,28 +2365,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>127.3</v>
+        <v>138.05</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="F4">
-        <v>143.31</v>
+        <v>141.52</v>
       </c>
       <c r="G4">
-        <v>0.5</v>
+        <v>0.517</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2248,25 +2397,25 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>171.21</v>
+        <v>157.37</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F5">
-        <v>143.31</v>
+        <v>141.87</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.483</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2274,28 +2423,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>145.48</v>
+        <v>126.14</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F6">
-        <v>143.31</v>
+        <v>140.03</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.517</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2303,28 +2452,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>150.6</v>
+        <v>123.34</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>143.31</v>
+        <v>137.61</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2335,25 +2484,25 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>146.89</v>
+        <v>140.39</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>143.31</v>
+        <v>137.16</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2361,28 +2510,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>130.56</v>
+        <v>160.99</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F9">
-        <v>143.31</v>
+        <v>139.74</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.504</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-1.8</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2390,28 +2539,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10">
+        <v>158.05</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10">
+        <v>137.53</v>
+      </c>
+      <c r="G10">
+        <v>0.492</v>
+      </c>
+      <c r="H10">
+        <v>-2</v>
+      </c>
+      <c r="I10">
         <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10">
-        <v>166.29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10">
-        <v>143.31</v>
-      </c>
-      <c r="G10">
-        <v>0.5</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2426,31 +2575,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2458,260 +2607,260 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>146.892</v>
+        <v>140.3866666666667</v>
       </c>
       <c r="E2">
-        <v>734.46</v>
+        <v>842.3200000000001</v>
       </c>
       <c r="F2">
-        <v>97.89999999999999</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>136.964</v>
+        <v>134.16</v>
       </c>
       <c r="E3">
-        <v>684.8200000000001</v>
+        <v>804.96</v>
       </c>
       <c r="F3">
-        <v>87.7</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>133.268</v>
+        <v>123.34</v>
       </c>
       <c r="E4">
-        <v>666.3399999999999</v>
+        <v>740.04</v>
       </c>
       <c r="F4">
-        <v>76</v>
+        <v>76.5</v>
       </c>
       <c r="G4">
         <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>133.032</v>
+        <v>131.14</v>
       </c>
       <c r="E5">
-        <v>665.16</v>
+        <v>786.84</v>
       </c>
       <c r="F5">
-        <v>72.89999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C6">
         <v>0.6</v>
       </c>
       <c r="D6">
-        <v>127.3</v>
+        <v>131.7066666666666</v>
       </c>
       <c r="E6">
-        <v>636.5</v>
+        <v>790.2399999999999</v>
       </c>
       <c r="F6">
-        <v>54.90000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D7">
-        <v>116.38</v>
+        <v>116.69</v>
       </c>
       <c r="E7">
-        <v>581.9000000000001</v>
+        <v>700.14</v>
       </c>
       <c r="F7">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="G7">
-        <v>6.2</v>
+        <v>9.700000000000001</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>120.484</v>
+        <v>115.04</v>
       </c>
       <c r="E8">
-        <v>602.42</v>
+        <v>690.2400000000001</v>
       </c>
       <c r="F8">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="G8">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>118.176</v>
+        <v>105.1166666666667</v>
       </c>
       <c r="E9">
-        <v>590.88</v>
+        <v>630.7</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G9">
-        <v>14.5</v>
+        <v>42.9</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D10">
-        <v>104.444</v>
+        <v>113.9266666666667</v>
       </c>
       <c r="E10">
-        <v>522.22</v>
+        <v>683.5599999999999</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
-        <v>67.2</v>
+        <v>34.9</v>
       </c>
       <c r="H10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2726,19 +2875,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2746,19 +2895,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2766,19 +2915,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2786,19 +2935,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2806,19 +2955,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2829,16 +2978,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2846,19 +2995,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>-3</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2866,19 +3015,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2886,19 +3035,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>-7</v>
+        <v>-13</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2906,19 +3055,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2928,122 +3077,137 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
         <v>7</v>
-      </c>
-      <c r="G3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -3062,100 +3226,115 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6">
+        <v>-3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7">
+        <v>-8</v>
+      </c>
+      <c r="C7">
+        <v>-12</v>
+      </c>
+      <c r="D7">
+        <v>-9</v>
+      </c>
+      <c r="E7">
+        <v>-15</v>
+      </c>
+      <c r="F7">
+        <v>-5</v>
+      </c>
+      <c r="G7">
+        <v>-3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-3</v>
+      </c>
+      <c r="C8">
+        <v>-3</v>
+      </c>
+      <c r="D8">
+        <v>-5</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>-9</v>
+      </c>
+      <c r="G8">
+        <v>-4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
         <v>4</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>-3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8">
-        <v>-8</v>
-      </c>
-      <c r="C8">
-        <v>-12</v>
-      </c>
-      <c r="D8">
-        <v>-9</v>
-      </c>
-      <c r="E8">
-        <v>-15</v>
-      </c>
-      <c r="F8">
-        <v>-5</v>
-      </c>
-      <c r="G8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>-1</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>-3</v>
+      </c>
+      <c r="G9">
+        <v>-13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>-1</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>-8</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>-7</v>
       </c>
-      <c r="G9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>-3</v>
-      </c>
-      <c r="C10">
-        <v>-3</v>
-      </c>
-      <c r="D10">
-        <v>-5</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>-9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>98</v>
+      <c r="G10">
+        <v>-15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
+++ b/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="118">
   <si>
     <t>Lox, Stocks and 2 Skattebooms!</t>
   </si>
@@ -52,7 +52,157 @@
     <t>Walnut Rushers</t>
   </si>
   <si>
-    <t>1-5-0</t>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>4-2-1</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>3-3-1</t>
+  </si>
+  <si>
+    <t>2-4-1</t>
+  </si>
+  <si>
+    <t>5-1-1</t>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>Wins Against Schedule</t>
+  </si>
+  <si>
+    <t>Record</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Expected Wins</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>1st Place</t>
+  </si>
+  <si>
+    <t>2nd Place</t>
+  </si>
+  <si>
+    <t>3rd Place</t>
+  </si>
+  <si>
+    <t>4th Place</t>
+  </si>
+  <si>
+    <t>5th Place</t>
+  </si>
+  <si>
+    <t>6th Place</t>
+  </si>
+  <si>
+    <t>7th Place</t>
+  </si>
+  <si>
+    <t>8th Place</t>
+  </si>
+  <si>
+    <t>9th Place</t>
+  </si>
+  <si>
+    <t>Chance of Making Playoffs</t>
+  </si>
+  <si>
+    <t>Week_1</t>
+  </si>
+  <si>
+    <t>Week_2</t>
+  </si>
+  <si>
+    <t>Week_3</t>
+  </si>
+  <si>
+    <t>Week_4</t>
+  </si>
+  <si>
+    <t>Week_5</t>
+  </si>
+  <si>
+    <t>Week_6</t>
+  </si>
+  <si>
+    <t>Week_7</t>
+  </si>
+  <si>
+    <t>Week_8</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Avg_Points_For</t>
+  </si>
+  <si>
+    <t>Team_Record</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Points_For</t>
+  </si>
+  <si>
+    <t>Avg_Opp_Win_Pct</t>
+  </si>
+  <si>
+    <t>Avg_Opp_LPI</t>
+  </si>
+  <si>
+    <t>Games_Remaining</t>
+  </si>
+  <si>
+    <t>Suhas Ketkar</t>
+  </si>
+  <si>
+    <t>Ashutosh Ketkar</t>
+  </si>
+  <si>
+    <t>Ritu Ketkar</t>
+  </si>
+  <si>
+    <t>Ayush Chivate</t>
+  </si>
+  <si>
+    <t>Melissa Sefl</t>
+  </si>
+  <si>
+    <t>Neel Ketkar</t>
+  </si>
+  <si>
+    <t>Akshata Ketkar</t>
+  </si>
+  <si>
+    <t>Dillan Ketkar</t>
+  </si>
+  <si>
+    <t>Vera Ketkar</t>
   </si>
   <si>
     <t>3-3-0</t>
@@ -64,147 +214,9 @@
     <t>2-4-0</t>
   </si>
   <si>
-    <t>3-2-1</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
     <t>5-1-0</t>
   </si>
   <si>
-    <t>2-3-1</t>
-  </si>
-  <si>
-    <t>4-1-1</t>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>Wins Against Schedule</t>
-  </si>
-  <si>
-    <t>Record</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Expected Wins</t>
-  </si>
-  <si>
-    <t>Difference</t>
-  </si>
-  <si>
-    <t>1st Place</t>
-  </si>
-  <si>
-    <t>2nd Place</t>
-  </si>
-  <si>
-    <t>3rd Place</t>
-  </si>
-  <si>
-    <t>4th Place</t>
-  </si>
-  <si>
-    <t>5th Place</t>
-  </si>
-  <si>
-    <t>6th Place</t>
-  </si>
-  <si>
-    <t>7th Place</t>
-  </si>
-  <si>
-    <t>8th Place</t>
-  </si>
-  <si>
-    <t>9th Place</t>
-  </si>
-  <si>
-    <t>Chance of Making Playoffs</t>
-  </si>
-  <si>
-    <t>Week_1</t>
-  </si>
-  <si>
-    <t>Week_2</t>
-  </si>
-  <si>
-    <t>Week_3</t>
-  </si>
-  <si>
-    <t>Week_4</t>
-  </si>
-  <si>
-    <t>Week_5</t>
-  </si>
-  <si>
-    <t>Week_6</t>
-  </si>
-  <si>
-    <t>Week_7</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Avg_Points_For</t>
-  </si>
-  <si>
-    <t>Team_Record</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Points_For</t>
-  </si>
-  <si>
-    <t>Avg_Opp_Win_Pct</t>
-  </si>
-  <si>
-    <t>Avg_Opp_LPI</t>
-  </si>
-  <si>
-    <t>Games_Remaining</t>
-  </si>
-  <si>
-    <t>Melissa Sefl</t>
-  </si>
-  <si>
-    <t>Suhas Ketkar</t>
-  </si>
-  <si>
-    <t>Ritu Ketkar</t>
-  </si>
-  <si>
-    <t>Ayush Chivate</t>
-  </si>
-  <si>
-    <t>Akshata Ketkar</t>
-  </si>
-  <si>
-    <t>Ashutosh Ketkar</t>
-  </si>
-  <si>
-    <t>Dillan Ketkar</t>
-  </si>
-  <si>
-    <t>Vera Ketkar</t>
-  </si>
-  <si>
-    <t>Neel Ketkar</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -229,61 +241,61 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
     <t>3-3</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.7-0.1</t>
-  </si>
-  <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.3-0.1</t>
-  </si>
-  <si>
-    <t>5.5-8.4-0.1</t>
-  </si>
-  <si>
-    <t>4.7-9.2-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>9-6</t>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>10.1-3.8-0.1</t>
+  </si>
+  <si>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.8-0.1</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
+    <t>10-5</t>
+  </si>
+  <si>
+    <t>9-4</t>
+  </si>
+  <si>
     <t>8-6</t>
   </si>
   <si>
-    <t>8-5</t>
+    <t>6-7</t>
   </si>
   <si>
     <t>6-8</t>
@@ -292,10 +304,7 @@
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
-    <t>5-10</t>
+    <t>4-11</t>
   </si>
   <si>
     <t>Owners</t>
@@ -307,33 +316,27 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
     <t>↑8</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↑6</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑5</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>↓2</t>
   </si>
   <si>
     <t>↓10</t>
   </si>
   <si>
-    <t>↓8</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -350,6 +353,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -771,7 +777,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -803,25 +809,25 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -829,31 +835,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
         <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
       </c>
       <c r="I4" t="s">
         <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -861,7 +867,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -870,22 +876,22 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>11</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>10</v>
-      </c>
-      <c r="J5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -896,28 +902,28 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -928,22 +934,22 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>12</v>
@@ -957,31 +963,31 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
         <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -992,7 +998,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1001,19 +1007,19 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1021,31 +1027,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1055,30 +1061,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1086,19 +1092,19 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>14</v>
@@ -1112,19 +1118,19 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>14</v>
@@ -1138,25 +1144,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>-15</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1167,22 +1173,22 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>-5</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1190,25 +1196,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>-5</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1219,22 +1225,22 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1242,25 +1248,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>3</v>
       </c>
-      <c r="G8">
+      <c r="H8" t="s">
         <v>2</v>
-      </c>
-      <c r="H8" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1268,25 +1274,25 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E9">
         <v>5</v>
       </c>
-      <c r="E9">
-        <v>-13</v>
-      </c>
       <c r="F9">
-        <v>-15</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1297,21 +1303,47 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>-13</v>
+      </c>
+      <c r="F10">
+        <v>-15</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
         <v>4</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>7</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>-3</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>-4</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1327,13 +1359,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1341,13 +1373,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>2.111111111111111</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1355,13 +1387,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2.666666666666667</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1372,10 +1404,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>2.666666666666667</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1386,10 +1418,10 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>2.777777777777778</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1397,13 +1429,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>3.111111111111111</v>
+        <v>3.444444444444445</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1411,13 +1443,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>3.222222222222222</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1425,10 +1457,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3.222222222222222</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -1439,13 +1471,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>3.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1453,10 +1485,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>3.555555555555555</v>
+        <v>4.111111111111111</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -1474,16 +1506,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1491,16 +1523,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>4.222222222222222</v>
+        <v>4.888888888888889</v>
       </c>
       <c r="D2">
-        <v>1.222222222222222</v>
+        <v>-0.1111111111111107</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1508,16 +1540,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>4.888888888888889</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>0.8888888888888893</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1525,13 +1557,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>3.555555555555555</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="D4">
-        <v>0.5555555555555554</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -1542,16 +1574,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>3.333333333333333</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="D5">
-        <v>0.3333333333333335</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1568,7 +1600,7 @@
         <v>-1</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1576,16 +1608,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>2.555555555555555</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>0.5555555555555554</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1593,16 +1625,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>2.333333333333333</v>
+        <v>2.888888888888889</v>
       </c>
       <c r="D8">
-        <v>0.3333333333333335</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1613,13 +1645,13 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>2.111111111111111</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D9">
-        <v>0.1111111111111112</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1630,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1.555555555555556</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D10">
-        <v>0.5555555555555556</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1651,63 +1683,63 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2">
-        <v>34.5</v>
+        <v>55.2</v>
       </c>
       <c r="C2">
-        <v>30.3</v>
+        <v>31.7</v>
       </c>
       <c r="D2">
-        <v>18.5</v>
+        <v>10.2</v>
       </c>
       <c r="E2">
-        <v>12.1</v>
+        <v>1.9</v>
       </c>
       <c r="F2">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="G2">
         <v>0.4</v>
       </c>
       <c r="H2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1716,33 +1748,33 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>95.40000000000001</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>41.2</v>
+        <v>36.2</v>
       </c>
       <c r="C3">
-        <v>29.2</v>
+        <v>42.3</v>
       </c>
       <c r="D3">
-        <v>15.2</v>
+        <v>13.6</v>
       </c>
       <c r="E3">
-        <v>9.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="F3">
-        <v>4.1</v>
+        <v>1.6</v>
       </c>
       <c r="G3">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1751,42 +1783,42 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>94.90000000000001</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="C4">
-        <v>16.5</v>
+        <v>17.4</v>
       </c>
       <c r="D4">
-        <v>23.5</v>
+        <v>39.1</v>
       </c>
       <c r="E4">
-        <v>27.9</v>
+        <v>21.8</v>
       </c>
       <c r="F4">
-        <v>18.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G4">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I4">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>76.5</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1794,69 +1826,69 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>10.1</v>
+        <v>0.9</v>
       </c>
       <c r="C5">
-        <v>14.1</v>
+        <v>5.5</v>
       </c>
       <c r="D5">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="E5">
-        <v>23.6</v>
+        <v>36.1</v>
       </c>
       <c r="F5">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>9.1</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
-        <v>72.2</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="C6">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="D6">
-        <v>16.4</v>
+        <v>7.6</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="F6">
-        <v>29.7</v>
+        <v>23.6</v>
       </c>
       <c r="G6">
-        <v>12.6</v>
+        <v>20.2</v>
       </c>
       <c r="H6">
-        <v>4.4</v>
+        <v>14.9</v>
       </c>
       <c r="I6">
-        <v>1.4</v>
+        <v>11.2</v>
       </c>
       <c r="J6">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="K6">
-        <v>51.4</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1867,31 +1899,31 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="D7">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>12.7</v>
       </c>
       <c r="F7">
-        <v>11.2</v>
+        <v>25.7</v>
       </c>
       <c r="G7">
-        <v>27.8</v>
+        <v>26.2</v>
       </c>
       <c r="H7">
-        <v>29.6</v>
+        <v>18.3</v>
       </c>
       <c r="I7">
-        <v>17.2</v>
+        <v>10.5</v>
       </c>
       <c r="J7">
-        <v>9.699999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1902,31 +1934,31 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="E8">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="F8">
         <v>8.699999999999999</v>
       </c>
       <c r="G8">
-        <v>28.8</v>
+        <v>19.7</v>
       </c>
       <c r="H8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I8">
-        <v>20.2</v>
+        <v>23.9</v>
       </c>
       <c r="J8">
-        <v>11.9</v>
+        <v>18.6</v>
       </c>
       <c r="K8">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1937,31 +1969,31 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E9">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>8.9</v>
       </c>
       <c r="G9">
-        <v>8.6</v>
+        <v>14.2</v>
       </c>
       <c r="H9">
-        <v>16</v>
+        <v>23.2</v>
       </c>
       <c r="I9">
-        <v>29.1</v>
+        <v>30.4</v>
       </c>
       <c r="J9">
-        <v>42.9</v>
+        <v>20.3</v>
       </c>
       <c r="K9">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1978,25 +2010,25 @@
         <v>0.1</v>
       </c>
       <c r="E10">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F10">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G10">
-        <v>11.2</v>
+        <v>6.7</v>
       </c>
       <c r="H10">
-        <v>19.4</v>
+        <v>13.8</v>
       </c>
       <c r="I10">
-        <v>31.6</v>
+        <v>22.3</v>
       </c>
       <c r="J10">
-        <v>34.9</v>
+        <v>54</v>
       </c>
       <c r="K10">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2006,59 +2038,65 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>93.10000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E2">
-        <v>57.9</v>
+        <v>62.2</v>
       </c>
       <c r="F2">
-        <v>73.8</v>
+        <v>74.7</v>
       </c>
       <c r="G2">
-        <v>93</v>
+        <v>92.7</v>
       </c>
       <c r="H2">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>99.2</v>
+      </c>
+      <c r="I2">
+        <v>99.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -2066,129 +2104,144 @@
         <v>99.7</v>
       </c>
       <c r="C3">
-        <v>96.2</v>
+        <v>97.3</v>
       </c>
       <c r="D3">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="E3">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="F3">
-        <v>97</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="G3">
-        <v>91.10000000000001</v>
+        <v>90</v>
       </c>
       <c r="H3">
-        <v>93.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="I3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>5.3</v>
+      </c>
+      <c r="C4">
+        <v>4.8</v>
+      </c>
+      <c r="D4">
+        <v>0.8</v>
+      </c>
+      <c r="E4">
+        <v>50.8</v>
+      </c>
+      <c r="F4">
+        <v>76.2</v>
+      </c>
+      <c r="G4">
+        <v>72.3</v>
+      </c>
+      <c r="H4">
+        <v>84.2</v>
+      </c>
+      <c r="I4">
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>92.80000000000001</v>
-      </c>
-      <c r="C4">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="D4">
+      <c r="B5">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="C5">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D5">
         <v>92.40000000000001</v>
       </c>
-      <c r="E4">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="F4">
-        <v>92.7</v>
-      </c>
-      <c r="G4">
-        <v>71.8</v>
-      </c>
-      <c r="H4">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
+      <c r="E5">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F5">
+        <v>93</v>
+      </c>
+      <c r="G5">
+        <v>71.2</v>
+      </c>
+      <c r="H5">
+        <v>56.49999999999999</v>
+      </c>
+      <c r="I5">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="C5">
-        <v>13.9</v>
-      </c>
-      <c r="D5">
-        <v>72</v>
-      </c>
-      <c r="E5">
-        <v>70.5</v>
-      </c>
-      <c r="F5">
-        <v>50.5</v>
-      </c>
-      <c r="G5">
-        <v>66.5</v>
-      </c>
-      <c r="H5">
-        <v>73.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B6">
-        <v>5.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="C6">
-        <v>3.6</v>
+        <v>16.2</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="E6">
-        <v>52.5</v>
+        <v>73.5</v>
       </c>
       <c r="F6">
-        <v>75.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>67.10000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H6">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>37.3</v>
+      </c>
+      <c r="I6">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>21.2</v>
+        <v>17.7</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>80.80000000000001</v>
       </c>
       <c r="D7">
-        <v>35.5</v>
+        <v>37.7</v>
       </c>
       <c r="E7">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="H7">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>18.5</v>
+      </c>
+      <c r="I7">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -2202,68 +2255,77 @@
         <v>0.1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F8">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="G8">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="H8">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>4.5</v>
+      </c>
+      <c r="I8">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>5.600000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E9">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="F9">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="G9">
-        <v>0.7000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H9">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>2.3</v>
+      </c>
+      <c r="I9">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="C10">
+        <v>1.6</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>1.1</v>
+      </c>
+      <c r="F10">
+        <v>2.7</v>
+      </c>
+      <c r="G10">
         <v>0.2</v>
-      </c>
-      <c r="D10">
-        <v>0.6</v>
-      </c>
-      <c r="E10">
-        <v>2.1</v>
-      </c>
-      <c r="F10">
-        <v>0.5</v>
-      </c>
-      <c r="G10">
-        <v>0.8999999999999999</v>
       </c>
       <c r="H10">
         <v>0.4</v>
+      </c>
+      <c r="I10">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -2278,28 +2340,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2307,28 +2369,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>113.93</v>
+        <v>135.11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="F2">
-        <v>139.78</v>
+        <v>141.87</v>
       </c>
       <c r="G2">
-        <v>0.517</v>
+        <v>0.582</v>
       </c>
       <c r="H2">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2336,28 +2398,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D3">
-        <v>140.03</v>
+        <v>131.96</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F3">
-        <v>143.04</v>
+        <v>136.75</v>
       </c>
       <c r="G3">
-        <v>0.546</v>
+        <v>0.483</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2368,25 +2430,25 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>138.05</v>
+        <v>132.45</v>
       </c>
       <c r="E4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F4">
-        <v>141.52</v>
+        <v>139.03</v>
       </c>
       <c r="G4">
-        <v>0.517</v>
+        <v>0.531</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2397,25 +2459,25 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5">
-        <v>157.37</v>
+        <v>146.97</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F5">
-        <v>141.87</v>
+        <v>138.13</v>
       </c>
       <c r="G5">
-        <v>0.483</v>
+        <v>0.473</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2423,28 +2485,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6">
+        <v>110.68</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>135.03</v>
+      </c>
+      <c r="G6">
+        <v>0.483</v>
+      </c>
+      <c r="H6">
+        <v>-0.4</v>
+      </c>
+      <c r="I6">
         <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6">
-        <v>126.14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6">
-        <v>140.03</v>
-      </c>
-      <c r="G6">
-        <v>0.517</v>
-      </c>
-      <c r="H6">
-        <v>0.2</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2452,28 +2514,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D7">
-        <v>123.34</v>
+        <v>155.89</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="F7">
-        <v>137.61</v>
+        <v>138.52</v>
       </c>
       <c r="G7">
-        <v>0.492</v>
+        <v>0.534</v>
       </c>
       <c r="H7">
-        <v>-0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2481,28 +2543,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>140.39</v>
+        <v>127.86</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F8">
-        <v>137.16</v>
+        <v>135.12</v>
       </c>
       <c r="G8">
-        <v>0.467</v>
+        <v>0.483</v>
       </c>
       <c r="H8">
-        <v>-1.2</v>
+        <v>-1.9</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2510,28 +2572,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D9">
-        <v>160.99</v>
+        <v>137.33</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>139.74</v>
+        <v>133.04</v>
       </c>
       <c r="G9">
-        <v>0.504</v>
+        <v>0.459</v>
       </c>
       <c r="H9">
-        <v>-1.8</v>
+        <v>-2.1</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2539,28 +2601,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10">
-        <v>158.05</v>
+        <v>157.95</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F10">
-        <v>137.53</v>
+        <v>138.72</v>
       </c>
       <c r="G10">
-        <v>0.492</v>
+        <v>0.52</v>
       </c>
       <c r="H10">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2575,118 +2637,118 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>140.3866666666667</v>
+        <v>135.3828571428571</v>
       </c>
       <c r="E2">
-        <v>842.3200000000001</v>
+        <v>947.6800000000001</v>
       </c>
       <c r="F2">
-        <v>95.39999999999999</v>
+        <v>99</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D3">
-        <v>134.16</v>
+        <v>137.3342857142857</v>
       </c>
       <c r="E3">
-        <v>804.96</v>
+        <v>961.34</v>
       </c>
       <c r="F3">
-        <v>94.89999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C4">
         <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>123.34</v>
+        <v>133.6228571428571</v>
       </c>
       <c r="E4">
-        <v>740.04</v>
+        <v>935.3599999999999</v>
       </c>
       <c r="F4">
-        <v>76.5</v>
+        <v>85.5</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2694,57 +2756,57 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>131.14</v>
+        <v>125.9742857142857</v>
       </c>
       <c r="E5">
-        <v>786.84</v>
+        <v>881.8200000000001</v>
       </c>
       <c r="F5">
-        <v>72.2</v>
+        <v>67.30000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>131.7066666666666</v>
+        <v>113.1057142857143</v>
       </c>
       <c r="E6">
-        <v>790.2399999999999</v>
+        <v>791.74</v>
       </c>
       <c r="F6">
-        <v>51.4</v>
+        <v>25.8</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2752,28 +2814,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>116.69</v>
+        <v>115.8057142857143</v>
       </c>
       <c r="E7">
-        <v>700.14</v>
+        <v>810.64</v>
       </c>
       <c r="F7">
-        <v>4.5</v>
+        <v>16.8</v>
       </c>
       <c r="G7">
-        <v>9.700000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2781,28 +2843,28 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>115.04</v>
+        <v>113.5285714285715</v>
       </c>
       <c r="E8">
-        <v>690.2400000000001</v>
+        <v>794.7000000000002</v>
       </c>
       <c r="F8">
-        <v>3.4</v>
+        <v>4.100000000000001</v>
       </c>
       <c r="G8">
-        <v>11.9</v>
+        <v>18.6</v>
       </c>
       <c r="H8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2810,28 +2872,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>105.1166666666667</v>
+        <v>109.5971428571429</v>
       </c>
       <c r="E9">
-        <v>630.7</v>
+        <v>767.1800000000001</v>
       </c>
       <c r="F9">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>42.9</v>
+        <v>20.3</v>
       </c>
       <c r="H9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2839,28 +2901,28 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D10">
-        <v>113.9266666666667</v>
+        <v>110.6828571428571</v>
       </c>
       <c r="E10">
-        <v>683.5599999999999</v>
+        <v>774.78</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="G10">
-        <v>34.9</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2875,19 +2937,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2901,13 +2963,13 @@
         <v>56</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2915,19 +2977,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2935,19 +2997,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2955,19 +3017,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2975,19 +3037,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>-3</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2998,16 +3060,16 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3015,19 +3077,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>52</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3038,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D9">
         <v>-13</v>
@@ -3047,7 +3109,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3058,16 +3120,16 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <v>-15</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3077,33 +3139,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>110</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3125,115 +3190,130 @@
       <c r="G2">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>-3</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>9</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
+      <c r="H4">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
+      <c r="B5">
         <v>-3</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
+      <c r="C5">
+        <v>-3</v>
+      </c>
+      <c r="D5">
+        <v>-5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>-9</v>
+      </c>
+      <c r="G5">
+        <v>-4</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="G4">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
         <v>-3</v>
       </c>
-      <c r="H6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3255,37 +3335,43 @@
       <c r="G7">
         <v>-3</v>
       </c>
-      <c r="H7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7">
+        <v>-5</v>
+      </c>
+      <c r="I7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>-5</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>-3</v>
       </c>
-      <c r="C8">
-        <v>-3</v>
-      </c>
-      <c r="D8">
-        <v>-5</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>-9</v>
-      </c>
-      <c r="G8">
-        <v>-4</v>
-      </c>
-      <c r="H8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8">
+        <v>-13</v>
+      </c>
+      <c r="I8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -3307,11 +3393,14 @@
       <c r="G9">
         <v>-13</v>
       </c>
-      <c r="H9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9">
+        <v>-13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -3333,8 +3422,11 @@
       <c r="G10">
         <v>-15</v>
       </c>
-      <c r="H10" t="s">
-        <v>102</v>
+      <c r="H10">
+        <v>-15</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
+++ b/data/leagues/Ketkar Fantasy Football 2026 2026.xlsx
@@ -259,19 +259,19 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>10.1-3.8-0.1</t>
+    <t>10.1-3.9-0.1</t>
   </si>
   <si>
     <t>9.4-4.5-0.1</t>
   </si>
   <si>
-    <t>8.4-5.5-0.1</t>
+    <t>8.5-5.5-0.1</t>
   </si>
   <si>
     <t>7.4-6.5-0.1</t>
   </si>
   <si>
-    <t>6.8-7.2-0.1</t>
+    <t>6.8-7.1-0.1</t>
   </si>
   <si>
     <t>6.2-7.7-0.1</t>
@@ -280,7 +280,7 @@
     <t>5.1-8.8-0.1</t>
   </si>
   <si>
-    <t>4.1-9.8-0.1</t>
+    <t>4.2-9.8-0.1</t>
   </si>
   <si>
     <t>10-4</t>
@@ -295,7 +295,7 @@
     <t>8-6</t>
   </si>
   <si>
-    <t>6-7</t>
+    <t>7-6</t>
   </si>
   <si>
     <t>6-8</t>
@@ -1721,22 +1721,22 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>55.2</v>
+        <v>56.8</v>
       </c>
       <c r="C2">
-        <v>31.7</v>
+        <v>30.2</v>
       </c>
       <c r="D2">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E2">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G2">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>99</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1756,22 +1756,22 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>36.2</v>
+        <v>34.6</v>
       </c>
       <c r="C3">
-        <v>42.3</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>13.6</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F3">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="G3">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1794,31 +1794,31 @@
         <v>7.2</v>
       </c>
       <c r="C4">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="D4">
-        <v>39.1</v>
+        <v>36.8</v>
       </c>
       <c r="E4">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="F4">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G4">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="K4">
-        <v>85.5</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1826,34 +1826,34 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C5">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="D5">
-        <v>24.8</v>
+        <v>23.7</v>
       </c>
       <c r="E5">
-        <v>36.1</v>
+        <v>38.1</v>
       </c>
       <c r="F5">
-        <v>18.7</v>
+        <v>19.2</v>
       </c>
       <c r="G5">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I5">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>67.3</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1861,34 +1861,34 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C6">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="D6">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="F6">
-        <v>23.6</v>
+        <v>24.4</v>
       </c>
       <c r="G6">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="H6">
-        <v>14.9</v>
+        <v>15.8</v>
       </c>
       <c r="I6">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J6">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>25.8</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1902,28 +1902,28 @@
         <v>0.7</v>
       </c>
       <c r="D7">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>12.7</v>
+        <v>11.5</v>
       </c>
       <c r="F7">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="G7">
-        <v>26.2</v>
+        <v>27</v>
       </c>
       <c r="H7">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="I7">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1940,25 +1940,25 @@
         <v>0.9</v>
       </c>
       <c r="E8">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="F8">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="G8">
-        <v>19.7</v>
+        <v>19.2</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I8">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="J8">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="K8">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1969,31 +1969,31 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E9">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="F9">
         <v>8.9</v>
       </c>
       <c r="G9">
-        <v>14.2</v>
+        <v>15.4</v>
       </c>
       <c r="H9">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
       <c r="I9">
-        <v>30.4</v>
+        <v>26.9</v>
       </c>
       <c r="J9">
-        <v>20.3</v>
+        <v>24</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2004,31 +2004,31 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D10">
         <v>0.1</v>
       </c>
       <c r="E10">
+        <v>0.4</v>
+      </c>
+      <c r="F10">
+        <v>2.2</v>
+      </c>
+      <c r="G10">
+        <v>6.5</v>
+      </c>
+      <c r="H10">
+        <v>15.8</v>
+      </c>
+      <c r="I10">
+        <v>25.2</v>
+      </c>
+      <c r="J10">
+        <v>49.7</v>
+      </c>
+      <c r="K10">
         <v>0.6</v>
-      </c>
-      <c r="F10">
-        <v>2.5</v>
-      </c>
-      <c r="G10">
-        <v>6.7</v>
-      </c>
-      <c r="H10">
-        <v>13.8</v>
-      </c>
-      <c r="I10">
-        <v>22.3</v>
-      </c>
-      <c r="J10">
-        <v>54</v>
-      </c>
-      <c r="K10">
-        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -2072,25 +2072,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>91.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="E2">
-        <v>62.2</v>
+        <v>60.8</v>
       </c>
       <c r="F2">
-        <v>74.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G2">
-        <v>92.7</v>
+        <v>93.10000000000001</v>
       </c>
       <c r="H2">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="I2">
         <v>99.3</v>
@@ -2101,28 +2101,28 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C3">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="D3">
         <v>99.8</v>
       </c>
       <c r="E3">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="F3">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="G3">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="H3">
         <v>96.89999999999999</v>
       </c>
-      <c r="G3">
-        <v>90</v>
-      </c>
-      <c r="H3">
-        <v>97.09999999999999</v>
-      </c>
       <c r="I3">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2130,28 +2130,28 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="C4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D4">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="E4">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="F4">
-        <v>76.2</v>
+        <v>76.3</v>
       </c>
       <c r="G4">
-        <v>72.3</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="H4">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="I4">
-        <v>85.3</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2159,28 +2159,28 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>95.09999999999999</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="C5">
-        <v>99.09999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="D5">
-        <v>92.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="E5">
-        <v>98.09999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="F5">
-        <v>93</v>
+        <v>93.5</v>
       </c>
       <c r="G5">
-        <v>71.2</v>
+        <v>68.5</v>
       </c>
       <c r="H5">
-        <v>56.49999999999999</v>
+        <v>55.60000000000001</v>
       </c>
       <c r="I5">
-        <v>65.40000000000001</v>
+        <v>68.30000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2188,28 +2188,28 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>73.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="C6">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="D6">
-        <v>71</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E6">
-        <v>73.5</v>
+        <v>72</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="G6">
-        <v>64.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="H6">
-        <v>37.3</v>
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2217,25 +2217,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="C7">
-        <v>80.80000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D7">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="F7">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G7">
         <v>5.5</v>
       </c>
       <c r="H7">
-        <v>18.5</v>
+        <v>16.3</v>
       </c>
       <c r="I7">
         <v>16.3</v>
@@ -2243,60 +2243,60 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
+        <v>2.8</v>
+      </c>
+      <c r="F8">
         <v>0.2</v>
       </c>
-      <c r="F8">
-        <v>4.6</v>
-      </c>
       <c r="G8">
-        <v>2.8</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="F9">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
       <c r="G9">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="H9">
-        <v>2.3</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="I9">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2304,28 +2304,28 @@
         <v>0</v>
       </c>
       <c r="B10">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="C10">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="E10">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F10">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="G10">
-        <v>0.2</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H10">
+        <v>0.3</v>
+      </c>
+      <c r="I10">
         <v>0.4</v>
-      </c>
-      <c r="I10">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -2681,7 +2681,7 @@
         <v>947.6800000000001</v>
       </c>
       <c r="F2">
-        <v>99</v>
+        <v>99.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>961.34</v>
       </c>
       <c r="F3">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2739,10 +2739,10 @@
         <v>935.3599999999999</v>
       </c>
       <c r="F4">
-        <v>85.5</v>
+        <v>85.7</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="s">
         <v>80</v>
@@ -2768,10 +2768,10 @@
         <v>881.8200000000001</v>
       </c>
       <c r="F5">
-        <v>67.30000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G5">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
         <v>81</v>
@@ -2797,10 +2797,10 @@
         <v>791.74</v>
       </c>
       <c r="F6">
-        <v>25.8</v>
+        <v>24.4</v>
       </c>
       <c r="G6">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="H6" t="s">
         <v>82</v>
@@ -2826,10 +2826,10 @@
         <v>810.64</v>
       </c>
       <c r="F7">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="G7">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
         <v>83</v>
@@ -2855,10 +2855,10 @@
         <v>794.7000000000002</v>
       </c>
       <c r="F8">
-        <v>4.100000000000001</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="G8">
-        <v>18.6</v>
+        <v>19.1</v>
       </c>
       <c r="H8" t="s">
         <v>84</v>
@@ -2884,10 +2884,10 @@
         <v>767.1800000000001</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G9">
-        <v>20.3</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
         <v>84</v>
@@ -2913,10 +2913,10 @@
         <v>774.78</v>
       </c>
       <c r="F10">
-        <v>0.7000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G10">
-        <v>54</v>
+        <v>49.7</v>
       </c>
       <c r="H10" t="s">
         <v>85</v>
@@ -3077,19 +3077,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D8">
         <v>-13</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3097,19 +3097,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>-13</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3344,60 +3344,60 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G8">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="H8">
         <v>-13</v>
       </c>
       <c r="I8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="D9">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>-3</v>
-      </c>
-      <c r="G9">
-        <v>-13</v>
       </c>
       <c r="H9">
         <v>-13</v>
       </c>
       <c r="I9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:9">
